--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>97822</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>100109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>724180.2738617097</v>
+        <v>724180</v>
       </c>
       <c r="R2" t="n">
-        <v>6393554.483765647</v>
+        <v>6393554</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>1992-07-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1992-07-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -813,12 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>103346</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -850,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>724180.2738617097</v>
+        <v>724180</v>
       </c>
       <c r="R3" t="n">
-        <v>6393554.483765647</v>
+        <v>6393554</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,19 +863,9 @@
           <t>1992-07-06</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1992-07-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -939,12 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>96225</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98471</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>724180.2738617097</v>
+        <v>724180</v>
       </c>
       <c r="R4" t="n">
-        <v>6393554.483765647</v>
+        <v>6393554</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,19 +974,9 @@
           <t>1992-07-06</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1992-07-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100109</v>
+        <v>100115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105704</v>
+        <v>105713</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98471</v>
+        <v>98477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100115</v>
+        <v>100119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105713</v>
+        <v>105725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98477</v>
+        <v>98480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100119</v>
+        <v>100125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105725</v>
+        <v>105734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98480</v>
+        <v>98483</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100125</v>
+        <v>100126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105734</v>
+        <v>105739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98483</v>
+        <v>98484</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100126</v>
+        <v>100153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105739</v>
+        <v>105767</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98484</v>
+        <v>98511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100153</v>
+        <v>100159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105767</v>
+        <v>105773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98511</v>
+        <v>98517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100159</v>
+        <v>100166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105773</v>
+        <v>105780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98517</v>
+        <v>98524</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100166</v>
+        <v>100170</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105780</v>
+        <v>105784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98524</v>
+        <v>98528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100170</v>
+        <v>100177</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105784</v>
+        <v>105791</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98528</v>
+        <v>98535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100180</v>
+        <v>100185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105794</v>
+        <v>105799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98538</v>
+        <v>98543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100185</v>
+        <v>100193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>106408955</v>
       </c>
       <c r="B3" t="n">
-        <v>105799</v>
+        <v>105807</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -909,7 +909,7 @@
         <v>106433016</v>
       </c>
       <c r="B4" t="n">
-        <v>98543</v>
+        <v>98551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 32666-2021 artfynd.xlsx
+++ b/artfynd/A 32666-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>106323209</v>
       </c>
       <c r="B2" t="n">
-        <v>100193</v>
+        <v>100666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106408955</v>
+        <v>106433016</v>
       </c>
       <c r="B3" t="n">
-        <v>105807</v>
+        <v>99010</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221423</v>
+        <v>219769</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Myskmadra</t>
+          <t>Vit skogslilja</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Galium odoratum</t>
+          <t>Cephalanthera longifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Fritsch</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>.  Inventeringsläger i GBF:s regi. Tjälder 1:13.</t>
+          <t>Inventeringsläger i GBF:s regi.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,11 +881,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Granskog, frisk, obetad</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -906,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106433016</v>
+        <v>106408955</v>
       </c>
       <c r="B4" t="n">
-        <v>98551</v>
+        <v>106329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -917,21 +912,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219769</v>
+        <v>221423</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vit skogslilja</t>
+          <t>Myskmadra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cephalanthera longifolia</t>
+          <t>Galium odoratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Fritsch</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -981,7 +976,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inventeringsläger i GBF:s regi.</t>
+          <t>.  Inventeringsläger i GBF:s regi. Tjälder 1:13.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -992,6 +987,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog, frisk, obetad</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
